--- a/init.xlsx
+++ b/init.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\euj1cob\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\euj1cob\TryoutMailGeneration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FE10AE-6E1E-4F0E-A351-6A695AB55C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BE2F23-56CD-471B-8AA6-12180C3EF72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="init" sheetId="1" r:id="rId1"/>
     <sheet name="Validlists" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,139 +37,151 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+  <si>
+    <t>Part_Numbers</t>
+  </si>
+  <si>
+    <t>SW_Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jira_Main_Task </t>
+  </si>
+  <si>
+    <t>Jira_TO_Task</t>
+  </si>
+  <si>
+    <t>PD_Version</t>
+  </si>
+  <si>
+    <t>CD_Version</t>
+  </si>
   <si>
     <t>ProductType</t>
   </si>
   <si>
+    <t>Base_SW</t>
+  </si>
+  <si>
+    <t>Release_Type</t>
+  </si>
+  <si>
+    <t>Docushare_CollectionID</t>
+  </si>
+  <si>
+    <t>Tryout_Location</t>
+  </si>
+  <si>
+    <t>FCID_Version</t>
+  </si>
+  <si>
+    <t>HW_List</t>
+  </si>
+  <si>
+    <t>Private_Key</t>
+  </si>
+  <si>
+    <t>Jira_Access_Token</t>
+  </si>
+  <si>
+    <t>Task_Name</t>
+  </si>
+  <si>
+    <t>Renault</t>
+  </si>
+  <si>
+    <t>SplUpd</t>
+  </si>
+  <si>
     <t>COB</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Private_key</t>
+  </si>
+  <si>
     <t>Nissan</t>
   </si>
   <si>
-    <t>SplUpd</t>
-  </si>
-  <si>
-    <t>Renault</t>
+    <t>Yes</t>
   </si>
   <si>
     <t>Image</t>
   </si>
   <si>
-    <t>Part_Numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jira_Main_Task </t>
-  </si>
-  <si>
-    <t>Jira_TO_Task</t>
-  </si>
-  <si>
-    <t>SW_Version</t>
-  </si>
-  <si>
-    <t>PD_Version</t>
-  </si>
-  <si>
-    <t>CD_Version</t>
-  </si>
-  <si>
-    <t>Base_SW</t>
-  </si>
-  <si>
-    <t>Release_Type</t>
-  </si>
-  <si>
-    <t>Docushare_CollectionID</t>
-  </si>
-  <si>
-    <t>Tryout_Location</t>
-  </si>
-  <si>
     <t>HI</t>
   </si>
   <si>
-    <t>FCID_Version</t>
-  </si>
-  <si>
-    <t>HW_List</t>
-  </si>
-  <si>
-    <t>Tryout_devices_AIVIT@Hi.xlsx</t>
-  </si>
-  <si>
-    <t>Tryout_devices_MMC@Cob.xlsx</t>
-  </si>
-  <si>
-    <t>Tryout_devices_AIVIT@Cob.xlsx</t>
-  </si>
-  <si>
-    <t>Private_key</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Private_Key</t>
-  </si>
-  <si>
     <t>P-IVI</t>
   </si>
   <si>
     <t>Mitsubishi</t>
   </si>
   <si>
-    <t>Task_Name</t>
-  </si>
-  <si>
-    <t>Tryout_devices_AIVI2_AIVIT@Cob.xlsx</t>
-  </si>
-  <si>
-    <t>Jira_Access_Token</t>
-  </si>
-  <si>
-    <t>V719</t>
-  </si>
-  <si>
-    <t>515119</t>
-  </si>
-  <si>
-    <t>Nissan P-IVI 23MY QLU@PgP1(CPW, RUS, PT2)</t>
-  </si>
-  <si>
-    <t>7.515.752.254</t>
-  </si>
-  <si>
-    <t>7.505.751.726</t>
-  </si>
-  <si>
-    <t>5526_211218</t>
-  </si>
-  <si>
-    <t>AIVI-92829</t>
-  </si>
-  <si>
-    <t>V03.56.0.0_PN00</t>
-  </si>
-  <si>
-    <t>V01.55.0.1_PN00_FINAL_KEY</t>
-  </si>
-  <si>
-    <t>AIVI-132039</t>
-  </si>
-  <si>
-    <t>&lt;JIRA ACCESS TOKEN&gt;</t>
+    <t>Tryout_devices@Hi.xlsx</t>
+  </si>
+  <si>
+    <t>Predecessor_PN</t>
+  </si>
+  <si>
+    <t>BaseSW_Task</t>
+  </si>
+  <si>
+    <t>Tryout_devices@Cob.xlsx</t>
+  </si>
+  <si>
+    <t>MDQ3NTU2MjMxNDI1OrC2uu6Z497KkR6bog5SMraT5E2w</t>
+  </si>
+  <si>
+    <t>7408_250909</t>
+  </si>
+  <si>
+    <t>7.505.752.208-01</t>
+  </si>
+  <si>
+    <t>7.515.753.298-01</t>
+  </si>
+  <si>
+    <t>7.515.753.354-01</t>
+  </si>
+  <si>
+    <t>7.503.751.943</t>
+  </si>
+  <si>
+    <t>7.515.753.189</t>
+  </si>
+  <si>
+    <t>7.515.753.228</t>
+  </si>
+  <si>
+    <t>AIVI-148185</t>
+  </si>
+  <si>
+    <t>AIVI-152006</t>
+  </si>
+  <si>
+    <t>V01.56.0.8_PN13</t>
+  </si>
+  <si>
+    <t>V03.62.0.0_PN10</t>
+  </si>
+  <si>
+    <t>Nissan A-IVI2 TSB12@PgP1 (new DDR4, Prio3)</t>
+  </si>
+  <si>
+    <t>546645</t>
+  </si>
+  <si>
+    <t>V791</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +326,26 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF172B4D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF172B4D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF404245"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -658,11 +693,15 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -723,9 +762,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -763,7 +802,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -869,7 +908,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1011,7 +1050,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1019,140 +1058,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C3" s="3"/>
+      <c r="I3" s="5"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J4" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J9" s="1"/>
+      <c r="C4" s="3"/>
+      <c r="I4" s="5"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C5" s="3"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L8" s="1"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L9" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1" xr:uid="{E7EB4ADC-836D-4F0C-9AE2-6A3DAF512F86}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
@@ -1160,43 +1238,43 @@
           <x14:formula1>
             <xm:f>Validlists!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:G4</xm:sqref>
+          <xm:sqref>H3:H4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D21E8E8A-BB11-4713-9FDD-3456217BA6EF}">
           <x14:formula1>
             <xm:f>Validlists!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I4</xm:sqref>
+          <xm:sqref>K2:K4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA865E63-0742-4A28-9310-AD10EFD43D05}">
           <x14:formula1>
             <xm:f>Validlists!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K4</xm:sqref>
+          <xm:sqref>M2:M4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8707A2D7-B555-4BD5-AA7E-C335F2290E27}">
           <x14:formula1>
             <xm:f>Validlists!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>M4</xm:sqref>
+          <xm:sqref>O4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77FF24C1-BEEE-4369-8AFE-FDD96698985E}">
           <x14:formula1>
             <xm:f>Validlists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>N2:N4</xm:sqref>
+          <xm:sqref>P2:P4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4B052F40-4537-4E4B-BFE4-8107A4D0BD9A}">
           <x14:formula1>
             <xm:f>Validlists!$A$2:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G2</xm:sqref>
+          <xm:sqref>H2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5A65316B-69D6-4C42-854F-4977ED166330}">
           <x14:formula1>
             <xm:f>Validlists!$D$2:$D$8</xm:f>
           </x14:formula1>
-          <xm:sqref>M2</xm:sqref>
+          <xm:sqref>O2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1206,83 +1284,81 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A46A450-3014-45DE-924D-CBC643654066}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{3A6B7CDC-FE3F-499E-BFDD-2A0E1901D066}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{0C4EDED5-35B5-4245-859A-486DB1378C2F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/init.xlsx
+++ b/init.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\euj1cob\TryoutMailGeneration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BE2F23-56CD-471B-8AA6-12180C3EF72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB074D4D-E57A-445C-95DA-48DBDC880EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Part_Numbers</t>
   </si>
@@ -114,9 +114,6 @@
     <t>HI</t>
   </si>
   <si>
-    <t>P-IVI</t>
-  </si>
-  <si>
     <t>Mitsubishi</t>
   </si>
   <si>
@@ -132,56 +129,47 @@
     <t>Tryout_devices@Cob.xlsx</t>
   </si>
   <si>
-    <t>MDQ3NTU2MjMxNDI1OrC2uu6Z497KkR6bog5SMraT5E2w</t>
-  </si>
-  <si>
     <t>7408_250909</t>
   </si>
   <si>
-    <t>7.505.752.208-01</t>
-  </si>
-  <si>
-    <t>7.515.753.298-01</t>
-  </si>
-  <si>
-    <t>7.515.753.354-01</t>
-  </si>
-  <si>
-    <t>7.503.751.943</t>
-  </si>
-  <si>
-    <t>7.515.753.189</t>
-  </si>
-  <si>
-    <t>7.515.753.228</t>
-  </si>
-  <si>
-    <t>AIVI-148185</t>
-  </si>
-  <si>
-    <t>AIVI-152006</t>
-  </si>
-  <si>
-    <t>V01.56.0.8_PN13</t>
-  </si>
-  <si>
-    <t>V03.62.0.0_PN10</t>
-  </si>
-  <si>
-    <t>Nissan A-IVI2 TSB12@PgP1 (new DDR4, Prio3)</t>
-  </si>
-  <si>
-    <t>546645</t>
-  </si>
-  <si>
-    <t>V791</t>
+    <t>V792</t>
+  </si>
+  <si>
+    <t>OTA2MzI4ODIzMDUxOmooBVDLfUCl+btK6gaFZTbUycvt</t>
+  </si>
+  <si>
+    <t>7.518.000.00U</t>
+  </si>
+  <si>
+    <t>7.518.000.00V</t>
+  </si>
+  <si>
+    <t>7.518.000.00W</t>
+  </si>
+  <si>
+    <t>V01.56.0.8_PN14</t>
+  </si>
+  <si>
+    <t>V03.62.0.0_PN11</t>
+  </si>
+  <si>
+    <t>AIVI-151990</t>
+  </si>
+  <si>
+    <t>7.518.000.00T</t>
+  </si>
+  <si>
+    <t>Nissan A-IVI2 SOP@PgP1 (DDR4, D sample, PP9)</t>
+  </si>
+  <si>
+    <t>AIVI-132039</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,6 +334,32 @@
     <font>
       <sz val="11"/>
       <color rgb="FF404245"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF172B4D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF172B4D"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -693,7 +707,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
@@ -701,6 +715,18 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1058,18 +1084,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="1" max="2" width="14.109375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.33203125" customWidth="1"/>
     <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.88671875" customWidth="1"/>
@@ -1084,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1108,7 +1133,7 @@
         <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -1136,121 +1161,133 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
       <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" t="s">
-        <v>45</v>
+      <c r="L2" s="9">
+        <v>546667</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>43</v>
+      <c r="Q2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="I3" s="5"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="8"/>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="5"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C5" s="3"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="I7" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="B6" s="6"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:18" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="6"/>
+      <c r="I7" s="7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I8" s="7"/>
+      <c r="J8" s="5"/>
       <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I9" s="7"/>
+      <c r="J9" s="5"/>
       <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I13" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="O2" r:id="rId1" xr:uid="{E7EB4ADC-836D-4F0C-9AE2-6A3DAF512F86}"/>
+    <hyperlink ref="O2" r:id="rId1" display="mailto:Tryout_devices@Cob.xlsx" xr:uid="{44CC67C8-976F-436A-9B24-F93E1356CB9A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7E8881AE-D75F-4547-9C31-D63BD5FC8409}">
-          <x14:formula1>
-            <xm:f>Validlists!$A$2:$A$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>H3:H4</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D21E8E8A-BB11-4713-9FDD-3456217BA6EF}">
           <x14:formula1>
             <xm:f>Validlists!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K4</xm:sqref>
+          <xm:sqref>K3:K4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DA865E63-0742-4A28-9310-AD10EFD43D05}">
           <x14:formula1>
             <xm:f>Validlists!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M4</xm:sqref>
+          <xm:sqref>M3:M4</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8707A2D7-B555-4BD5-AA7E-C335F2290E27}">
           <x14:formula1>
@@ -1262,19 +1299,13 @@
           <x14:formula1>
             <xm:f>Validlists!$E$2:$E$3</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P4</xm:sqref>
+          <xm:sqref>P3:P4</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4B052F40-4537-4E4B-BFE4-8107A4D0BD9A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7E8881AE-D75F-4547-9C31-D63BD5FC8409}">
           <x14:formula1>
-            <xm:f>Validlists!$A$2:$A$6</xm:f>
+            <xm:f>Validlists!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>H2</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5A65316B-69D6-4C42-854F-4977ED166330}">
-          <x14:formula1>
-            <xm:f>Validlists!$D$2:$D$8</xm:f>
-          </x14:formula1>
-          <xm:sqref>O2</xm:sqref>
+          <xm:sqref>H2:H4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1319,7 +1350,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
@@ -1336,24 +1367,22 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
       <c r="D6" s="2"/>
     </row>
   </sheetData>
